--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -12969,7 +12969,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>成都高新宜家家居新能源空间</t>
+          <t>成都东安天街城市中心店</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
+          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>成都东安天街城市中心店</t>
+          <t>成都高新宜家家居新能源空间</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
+          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>广州森那美富悦4S中心</t>
+          <t>广州保利时光里新能源空间</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
+          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>广州保利时光里新能源空间</t>
+          <t>广州森那美富悦4S中心</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -13272,7 +13272,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
+          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -13289,7 +13289,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>深圳标林卫星店</t>
+          <t>深圳星河WORLD.COCO Park新能源空间</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>深圳德顺行龙岗卫星店</t>
+          <t>深圳标林卫星店</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
+          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>深圳星河WORLD.COCO Park新能源空间</t>
+          <t>深圳德顺行龙岗卫星店</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
+          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>昆山青阳万达广场新能源空间</t>
+          <t>苏州吴江吾悦广场新能源空间</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -13528,12 +13528,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>苏州市昆山市青阳北路234号</t>
+          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -13545,7 +13545,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>苏州吴江吾悦广场新能源空间</t>
+          <t>昆山青阳万达广场新能源空间</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
+          <t>苏州市昆山市青阳北路234号</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -15162,22 +15162,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -15187,29 +15187,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
@@ -15231,17 +15231,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
@@ -15263,17 +15263,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -15283,7 +15283,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
@@ -15295,17 +15295,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -15315,29 +15315,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -15347,29 +15347,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -15379,29 +15379,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
@@ -15423,17 +15423,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -15443,29 +15443,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -15475,29 +15475,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15507,7 +15507,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
@@ -15519,17 +15519,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15539,29 +15539,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15571,29 +15571,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15603,29 +15603,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -15635,29 +15635,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15667,29 +15667,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -15699,7 +15699,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
         </is>
       </c>
     </row>
@@ -15711,17 +15711,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15731,29 +15731,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -15763,7 +15763,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
@@ -15807,17 +15807,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -15827,29 +15827,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -15859,29 +15859,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -15891,29 +15891,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -15923,29 +15923,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -15955,29 +15955,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -15987,14 +15987,14 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -16004,12 +16004,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -16058,22 +16058,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -16083,7 +16083,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
     </row>
@@ -16122,22 +16122,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心</t>
+          <t>理想汽车滨州北海大道汽车城零售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -16147,7 +16147,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
     </row>
@@ -16159,17 +16159,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -16179,7 +16179,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
     </row>
@@ -16191,17 +16191,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售展厅</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -16211,29 +16211,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -16250,22 +16250,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -16282,22 +16282,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -16319,17 +16319,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -16351,17 +16351,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -16383,17 +16383,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -16415,17 +16415,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -16442,22 +16442,22 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16479,17 +16479,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -16506,22 +16506,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16543,17 +16543,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16570,22 +16570,22 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -16639,17 +16639,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16666,22 +16666,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16703,17 +16703,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16730,22 +16730,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16762,22 +16762,22 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -16799,17 +16799,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16826,22 +16826,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -16858,22 +16858,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -16890,22 +16890,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16927,17 +16927,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -16954,22 +16954,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -16986,22 +16986,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -17023,17 +17023,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -17050,22 +17050,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -17082,22 +17082,22 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -17119,17 +17119,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -17146,22 +17146,22 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -17183,17 +17183,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -17215,17 +17215,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都成双大道</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -17242,22 +17242,22 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -17274,22 +17274,22 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -17311,17 +17311,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -17343,17 +17343,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -17370,22 +17370,22 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东阳新光汇）</t>
+          <t>赣州万象城体验店</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（见大未来天地）</t>
+          <t>赣州万象城体验店L141</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -17395,29 +17395,29 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 70%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店</t>
+          <t>华为授权体验店（东阳新光汇）</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店L141</t>
+          <t>华为授权体验店（见大未来天地）</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -17427,29 +17427,29 @@
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 70%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞麻涌交付中心</t>
+          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞高埗交付中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -17459,29 +17459,29 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 75%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙君尚零售展厅</t>
+          <t>华为智能生活馆•保定先天下</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙万象城零售中心</t>
+          <t>华为智能生活馆•保定北国先天下</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -17491,29 +17491,29 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定先天下</t>
+          <t>理想汽车长沙君尚零售展厅</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定北国先天下</t>
+          <t>理想汽车长沙万象城零售中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -17523,29 +17523,29 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
+          <t>理想汽车东莞麻涌交付中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>理想汽车东莞高埗交付中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -17555,7 +17555,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 75%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -11219,7 +11219,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创茂）</t>
+          <t>华为智能生活馆•青岛金狮广场</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -11234,12 +11234,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号</t>
+          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛金狮广场</t>
+          <t>华为授权体验店（融创茂）</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
+          <t>山东省青岛市黄岛区滨海大道2777号</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -13225,7 +13225,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>广州白云万达新能源空间</t>
+          <t>广州森那美富悦4S中心</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -13240,12 +13240,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市白云区三元里街道云城东路501号</t>
+          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>连续在档 2 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13257,7 +13257,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>广州森那美富悦4S中心</t>
+          <t>广州白云万达新能源空间</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -13272,12 +13272,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
+          <t>广东省广州市白云区三元里街道云城东路501号</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -13321,7 +13321,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>深圳标林卫星店</t>
+          <t>深圳德顺行龙岗卫星店</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
+          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>深圳德顺行龙岗卫星店</t>
+          <t>深圳标林卫星店</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
+          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>苏州吴江吾悦广场新能源空间</t>
+          <t>昆山青阳万达广场新能源空间</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -13528,12 +13528,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
+          <t>苏州市昆山市青阳北路234号</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13545,7 +13545,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>昆山青阳万达广场新能源空间</t>
+          <t>苏州吴江吾悦广场新能源空间</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>苏州市昆山市青阳北路234号</t>
+          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海金桥啦啦宝都</t>
+          <t>蔚来空间 | 上海徐汇万科广场</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -14616,7 +14616,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
+          <t>上海市徐汇区沪闵路9191号L1-17室</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海徐汇万科广场</t>
+          <t>蔚来空间 | 上海金桥啦啦宝都</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>上海市徐汇区沪闵路9191号L1-17室</t>
+          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -15167,17 +15167,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -15187,29 +15187,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
@@ -15231,17 +15231,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -15251,29 +15251,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -15283,29 +15283,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -15315,29 +15315,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
@@ -15359,17 +15359,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
@@ -15391,17 +15391,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
@@ -15423,17 +15423,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -15443,7 +15443,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
@@ -15482,22 +15482,22 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15507,29 +15507,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15539,7 +15539,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
@@ -15551,17 +15551,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15571,7 +15571,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
@@ -15583,17 +15583,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15603,29 +15603,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -15635,29 +15635,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15667,29 +15667,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -15699,29 +15699,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15731,29 +15731,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -15763,7 +15763,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
@@ -15807,17 +15807,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -15827,29 +15827,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -15859,7 +15859,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
@@ -15898,22 +15898,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -15923,7 +15923,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
@@ -15935,17 +15935,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -15955,29 +15955,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -15987,7 +15987,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
@@ -15999,17 +15999,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
@@ -16031,17 +16031,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售展厅</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -16051,29 +16051,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -16083,29 +16083,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -16115,29 +16115,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -16147,7 +16147,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
     </row>
@@ -16159,17 +16159,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -16179,7 +16179,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
     </row>
@@ -16191,17 +16191,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -16211,29 +16211,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -16250,22 +16250,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -16282,22 +16282,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -16319,17 +16319,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -16346,22 +16346,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -16383,17 +16383,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -16415,17 +16415,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -16447,17 +16447,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16479,17 +16479,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -16506,22 +16506,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16543,17 +16543,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都成双大道</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16570,22 +16570,22 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -16607,17 +16607,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -16634,22 +16634,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16666,22 +16666,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16703,17 +16703,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16735,17 +16735,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16767,17 +16767,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -16799,17 +16799,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16826,22 +16826,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -16858,22 +16858,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -16895,17 +16895,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16927,17 +16927,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -16954,22 +16954,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -16991,17 +16991,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -17018,22 +17018,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -17050,22 +17050,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -17119,17 +17119,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -17151,17 +17151,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -17178,22 +17178,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -17215,17 +17215,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -17242,22 +17242,22 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -17316,12 +17316,12 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -17343,17 +17343,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -17370,22 +17370,22 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店</t>
+          <t>华为授权体验店（东阳新光汇）</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店L141</t>
+          <t>华为授权体验店（见大未来天地）</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -17395,29 +17395,29 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 70%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东阳新光汇）</t>
+          <t>赣州万象城体验店</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（见大未来天地）</t>
+          <t>赣州万象城体验店L141</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -17427,29 +17427,29 @@
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 70%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
+          <t>华为智能生活馆•保定先天下</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>华为智能生活馆•保定北国先天下</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -17459,29 +17459,29 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定先天下</t>
+          <t>理想汽车长沙君尚零售展厅</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定北国先天下</t>
+          <t>理想汽车长沙万象城零售中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -17491,29 +17491,29 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙君尚零售展厅</t>
+          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙万象城零售中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -17523,7 +17523,7 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -11219,7 +11219,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛金狮广场</t>
+          <t>华为授权体验店（融创茂）</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -11234,12 +11234,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
+          <t>山东省青岛市黄岛区滨海大道2777号</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创茂）</t>
+          <t>华为智能生活馆•青岛金狮广场</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号</t>
+          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -12201,7 +12201,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>西红门镇金时大街7号院3号楼一层101</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>西红门镇金时大街7号院3号楼一层101</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -12297,7 +12297,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市宝安区机场综合楼服务中心</t>
+          <t>小米汽车广东深圳宝安区沙井京基百纳</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车交付中心(机场综合楼店)</t>
+          <t>沙井京基百纳广场一楼橙厅</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期；本期存在高相似店名「小米汽车广东省深圳市宝安区机场综合楼零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区沙井京基百纳</t>
+          <t>小米汽车广东省深圳市宝安区机场综合楼服务中心</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -12344,12 +12344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>沙井京基百纳广场一楼橙厅</t>
+          <t>小米汽车交付中心(机场综合楼店)</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「小米汽车广东省深圳市宝安区机场综合楼零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>成都东安天街城市中心店</t>
+          <t>成都高新宜家家居新能源空间</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
+          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>成都高新宜家家居新能源空间</t>
+          <t>成都东安天街城市中心店</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
+          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>广州保利时光里新能源空间</t>
+          <t>广州森那美富悦4S中心</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
+          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -13225,7 +13225,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>广州森那美富悦4S中心</t>
+          <t>广州白云万达新能源空间</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -13240,12 +13240,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
+          <t>广东省广州市白云区三元里街道云城东路501号</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -13257,7 +13257,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>广州白云万达新能源空间</t>
+          <t>广州保利时光里新能源空间</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -13272,12 +13272,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市白云区三元里街道云城东路501号</t>
+          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>连续在档 2 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13321,7 +13321,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>深圳德顺行龙岗卫星店</t>
+          <t>深圳标林卫星店</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
+          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>深圳标林卫星店</t>
+          <t>深圳德顺行龙岗卫星店</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
+          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>昆山青阳万达广场新能源空间</t>
+          <t>苏州吴江吾悦广场新能源空间</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -13528,12 +13528,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>苏州市昆山市青阳北路234号</t>
+          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -13545,7 +13545,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>苏州吴江吾悦广场新能源空间</t>
+          <t>昆山青阳万达广场新能源空间</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
+          <t>苏州市昆山市青阳北路234号</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -15167,17 +15167,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -15187,7 +15187,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
@@ -15199,17 +15199,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -15219,29 +15219,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -15251,29 +15251,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -15283,29 +15283,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -15315,29 +15315,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
@@ -15359,17 +15359,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -15379,29 +15379,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
@@ -15428,12 +15428,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -15443,29 +15443,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -15475,7 +15475,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
@@ -15487,17 +15487,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15507,29 +15507,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15539,7 +15539,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
@@ -15578,22 +15578,22 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15603,7 +15603,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
@@ -15615,17 +15615,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -15635,29 +15635,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
@@ -15711,17 +15711,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15731,29 +15731,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -15763,29 +15763,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -15795,7 +15795,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
@@ -15834,22 +15834,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -15859,29 +15859,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -15891,29 +15891,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -15923,29 +15923,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -15955,29 +15955,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -15987,29 +15987,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -16019,14 +16019,14 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -16036,12 +16036,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
     </row>
@@ -16063,17 +16063,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -16083,29 +16083,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -16115,29 +16115,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -16147,29 +16147,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -16179,7 +16179,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
     </row>
@@ -16191,17 +16191,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售展厅</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -16211,29 +16211,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -16255,17 +16255,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -16282,22 +16282,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -16319,17 +16319,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -16351,17 +16351,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -16415,17 +16415,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -16447,17 +16447,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16479,17 +16479,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -16511,17 +16511,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16538,7 +16538,7 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -16548,12 +16548,12 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16575,17 +16575,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -16607,17 +16607,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -16634,22 +16634,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16666,22 +16666,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16703,17 +16703,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16735,17 +16735,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16767,17 +16767,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -16794,22 +16794,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16826,22 +16826,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -16858,22 +16858,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -16890,7 +16890,7 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -16900,12 +16900,12 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16922,22 +16922,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -16959,17 +16959,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都成双大道</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -16991,17 +16991,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -17018,22 +17018,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -17050,22 +17050,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -17087,17 +17087,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -17114,22 +17114,22 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -17151,17 +17151,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -17178,22 +17178,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -17215,17 +17215,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -17242,22 +17242,22 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -17274,22 +17274,22 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -17311,17 +17311,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -17338,7 +17338,7 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -17348,12 +17348,12 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -17471,17 +17471,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙君尚零售展厅</t>
+          <t>理想汽车东莞麻涌交付中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙万象城零售中心</t>
+          <t>理想汽车东莞高埗交付中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -17491,29 +17491,29 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 75%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
+          <t>理想汽车长沙君尚零售展厅</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>理想汽车长沙万象城零售中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -17523,29 +17523,29 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞麻涌交付中心</t>
+          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞高埗交付中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -17555,7 +17555,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 75%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -12297,7 +12297,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区沙井京基百纳</t>
+          <t>小米汽车广东省深圳市宝安区机场综合楼服务中心</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>沙井京基百纳广场一楼橙厅</t>
+          <t>小米汽车交付中心(机场综合楼店)</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「小米汽车广东省深圳市宝安区机场综合楼零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市宝安区机场综合楼服务中心</t>
+          <t>小米汽车广东深圳宝安区沙井京基百纳</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -12344,12 +12344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车交付中心(机场综合楼店)</t>
+          <t>沙井京基百纳广场一楼橙厅</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期；本期存在高相似店名「小米汽车广东省深圳市宝安区机场综合楼零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>成都高新宜家家居新能源空间</t>
+          <t>成都东安天街城市中心店</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
+          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>成都东安天街城市中心店</t>
+          <t>成都高新宜家家居新能源空间</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
+          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>广州森那美富悦4S中心</t>
+          <t>广州白云万达新能源空间</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -13208,12 +13208,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
+          <t>广东省广州市白云区三元里街道云城东路501号</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -13225,7 +13225,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>广州白云万达新能源空间</t>
+          <t>广州森那美富悦4S中心</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -13240,12 +13240,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市白云区三元里街道云城东路501号</t>
+          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>连续在档 2 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海徐汇万科广场</t>
+          <t>蔚来空间 | 上海金桥啦啦宝都</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -14616,7 +14616,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>上海市徐汇区沪闵路9191号L1-17室</t>
+          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海金桥啦啦宝都</t>
+          <t>蔚来空间 | 上海徐汇万科广场</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
+          <t>上海市徐汇区沪闵路9191号L1-17室</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -15167,17 +15167,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -15187,7 +15187,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
@@ -15204,12 +15204,12 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -15219,29 +15219,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -15251,29 +15251,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -15283,29 +15283,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -15315,29 +15315,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -15347,29 +15347,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -15379,29 +15379,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -15411,29 +15411,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -15443,7 +15443,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
         </is>
       </c>
     </row>
@@ -15455,17 +15455,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -15475,14 +15475,14 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -15492,12 +15492,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15507,7 +15507,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
@@ -15546,22 +15546,22 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15571,29 +15571,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15603,29 +15603,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -15635,7 +15635,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
@@ -15647,17 +15647,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
         </is>
       </c>
     </row>
@@ -15706,22 +15706,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15731,29 +15731,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -15763,29 +15763,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -15795,29 +15795,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -15827,29 +15827,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -15859,7 +15859,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -15871,17 +15871,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -15891,29 +15891,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -15923,29 +15923,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
@@ -15967,17 +15967,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -15987,29 +15987,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -16019,29 +16019,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
@@ -16063,17 +16063,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售展厅</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -16083,7 +16083,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
     </row>
@@ -16122,22 +16122,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -16147,29 +16147,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -16179,29 +16179,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -16211,29 +16211,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -16255,17 +16255,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -16282,22 +16282,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -16319,17 +16319,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -16346,22 +16346,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -16383,17 +16383,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -16410,22 +16410,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -16447,17 +16447,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16474,22 +16474,22 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -16506,22 +16506,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16538,22 +16538,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16570,22 +16570,22 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -16639,17 +16639,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16666,22 +16666,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16698,22 +16698,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都成双大道</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16735,17 +16735,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16767,17 +16767,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -16794,22 +16794,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16826,22 +16826,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -16858,7 +16858,7 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -16868,12 +16868,12 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -16890,22 +16890,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16922,22 +16922,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -16986,22 +16986,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -17023,17 +17023,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -17050,22 +17050,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -17087,17 +17087,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -17114,22 +17114,22 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -17146,22 +17146,22 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -17183,17 +17183,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -17215,17 +17215,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -17242,22 +17242,22 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -17279,17 +17279,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -17311,17 +17311,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -17338,22 +17338,22 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -17466,22 +17466,22 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞麻涌交付中心</t>
+          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞高埗交付中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 75%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>
@@ -17530,22 +17530,22 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
+          <t>理想汽车东莞麻涌交付中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>理想汽车东莞高埗交付中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -17555,7 +17555,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 75%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -11219,7 +11219,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创茂）</t>
+          <t>华为智能生活馆•青岛金狮广场</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -11234,12 +11234,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号</t>
+          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛金狮广场</t>
+          <t>华为授权体验店（融创茂）</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
+          <t>山东省青岛市黄岛区滨海大道2777号</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>深圳星河WORLD.COCO Park新能源空间</t>
+          <t>深圳标林卫星店</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
+          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>深圳标林卫星店</t>
+          <t>深圳德顺行龙岗卫星店</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
+          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>深圳德顺行龙岗卫星店</t>
+          <t>深圳星河WORLD.COCO Park新能源空间</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -14601,7 +14601,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海金桥啦啦宝都</t>
+          <t>蔚来空间 | 上海徐汇万科广场</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -14616,7 +14616,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
+          <t>上海市徐汇区沪闵路9191号L1-17室</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海徐汇万科广场</t>
+          <t>蔚来空间 | 上海金桥啦啦宝都</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>上海市徐汇区沪闵路9191号L1-17室</t>
+          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -15162,22 +15162,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -15187,29 +15187,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -15219,14 +15219,14 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -15236,12 +15236,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
@@ -15263,17 +15263,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -15283,7 +15283,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
@@ -15295,17 +15295,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -15315,29 +15315,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
@@ -15359,17 +15359,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -15379,29 +15379,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -15411,29 +15411,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -15443,7 +15443,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
@@ -15455,17 +15455,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -15475,29 +15475,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15507,29 +15507,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15539,29 +15539,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15571,29 +15571,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15603,29 +15603,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -15635,29 +15635,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
@@ -15679,17 +15679,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -15699,29 +15699,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15731,29 +15731,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -15763,29 +15763,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -15795,29 +15795,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -15827,7 +15827,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
@@ -15839,17 +15839,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -15859,7 +15859,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
@@ -15871,17 +15871,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -15891,7 +15891,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
@@ -15903,17 +15903,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -15923,29 +15923,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
@@ -15967,17 +15967,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -15987,7 +15987,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
@@ -15999,17 +15999,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -16019,29 +16019,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
     </row>
@@ -16063,17 +16063,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -16083,7 +16083,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
     </row>
@@ -16095,17 +16095,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售展厅</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -16115,29 +16115,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -16147,29 +16147,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -16179,29 +16179,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
     </row>
@@ -16223,17 +16223,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -16250,22 +16250,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -16282,7 +16282,7 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -16292,12 +16292,12 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -16319,17 +16319,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -16346,22 +16346,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -16383,17 +16383,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -16410,22 +16410,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -16447,17 +16447,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16474,22 +16474,22 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -16506,22 +16506,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16538,22 +16538,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都成双大道</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16570,22 +16570,22 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -16607,17 +16607,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -16639,17 +16639,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16671,17 +16671,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16698,22 +16698,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16730,22 +16730,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16767,17 +16767,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -16794,22 +16794,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16831,17 +16831,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -16858,22 +16858,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -16890,22 +16890,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16927,17 +16927,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -16959,17 +16959,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -16986,22 +16986,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -17023,17 +17023,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -17060,12 +17060,12 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -17082,22 +17082,22 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -17119,17 +17119,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -17146,22 +17146,22 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -17183,17 +17183,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -17215,17 +17215,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -17279,17 +17279,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -17306,22 +17306,22 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -17338,7 +17338,7 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -17348,12 +17348,12 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -17370,22 +17370,22 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东阳新光汇）</t>
+          <t>赣州万象城体验店</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（见大未来天地）</t>
+          <t>赣州万象城体验店L141</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -17395,29 +17395,29 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 70%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店</t>
+          <t>华为授权体验店（东阳新光汇）</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店L141</t>
+          <t>华为授权体验店（见大未来天地）</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -17427,7 +17427,7 @@
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 70%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -11219,7 +11219,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛金狮广场</t>
+          <t>华为授权体验店（融创茂）</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -11234,12 +11234,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
+          <t>山东省青岛市黄岛区滨海大道2777号</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创茂）</t>
+          <t>华为智能生活馆•青岛金狮广场</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号</t>
+          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -12201,7 +12201,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>西红门镇金时大街7号院3号楼一层101</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>西红门镇金时大街7号院3号楼一层101</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -13225,7 +13225,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>广州森那美富悦4S中心</t>
+          <t>广州保利时光里新能源空间</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -13240,7 +13240,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
+          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>广州保利时光里新能源空间</t>
+          <t>广州森那美富悦4S中心</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -13272,7 +13272,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
+          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -13289,7 +13289,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>深圳标林卫星店</t>
+          <t>深圳德顺行龙岗卫星店</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
+          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>深圳德顺行龙岗卫星店</t>
+          <t>深圳星河WORLD.COCO Park新能源空间</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>深圳星河WORLD.COCO Park新能源空间</t>
+          <t>深圳标林卫星店</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
+          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -14601,7 +14601,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海徐汇万科广场</t>
+          <t>蔚来空间 | 上海金桥啦啦宝都</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -14616,7 +14616,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>上海市徐汇区沪闵路9191号L1-17室</t>
+          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海金桥啦啦宝都</t>
+          <t>蔚来空间 | 上海徐汇万科广场</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
+          <t>上海市徐汇区沪闵路9191号L1-17室</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -15167,17 +15167,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -15187,29 +15187,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -15219,29 +15219,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -15251,29 +15251,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -15283,29 +15283,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -15315,7 +15315,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
@@ -15327,17 +15327,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -15347,29 +15347,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -15379,29 +15379,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
@@ -15423,17 +15423,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -15443,7 +15443,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -15487,17 +15487,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15507,29 +15507,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15539,29 +15539,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15571,29 +15571,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15603,29 +15603,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -15635,7 +15635,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
@@ -15647,17 +15647,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15667,29 +15667,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -15699,29 +15699,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15731,7 +15731,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
@@ -15743,17 +15743,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -15763,7 +15763,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
@@ -15775,17 +15775,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -15795,29 +15795,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -15827,7 +15827,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
@@ -15839,17 +15839,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -15859,29 +15859,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -15891,29 +15891,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -15923,29 +15923,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -15955,29 +15955,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -15987,29 +15987,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -16019,29 +16019,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
     </row>
@@ -16063,17 +16063,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -16083,14 +16083,14 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -16100,12 +16100,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -16115,7 +16115,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
     </row>
@@ -16127,17 +16127,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售展厅</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -16147,29 +16147,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -16179,7 +16179,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
     </row>
@@ -16191,17 +16191,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -16211,29 +16211,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -16255,17 +16255,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -16287,17 +16287,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -16319,17 +16319,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -16346,22 +16346,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -16383,17 +16383,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -16415,17 +16415,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -16447,17 +16447,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16474,22 +16474,22 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -16511,17 +16511,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16538,22 +16538,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16570,22 +16570,22 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -16602,7 +16602,7 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -16612,12 +16612,12 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -16634,22 +16634,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16671,17 +16671,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16698,22 +16698,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16730,22 +16730,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16767,17 +16767,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -16794,22 +16794,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16831,17 +16831,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -16868,12 +16868,12 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -16895,17 +16895,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16927,17 +16927,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -16954,22 +16954,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -16991,17 +16991,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -17018,22 +17018,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -17055,17 +17055,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -17082,22 +17082,22 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -17114,22 +17114,22 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -17151,17 +17151,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -17178,22 +17178,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都成双大道</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -17215,17 +17215,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -17242,22 +17242,22 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -17279,17 +17279,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -17306,22 +17306,22 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -17338,22 +17338,22 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -17434,22 +17434,22 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定先天下</t>
+          <t>理想汽车长沙君尚零售展厅</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定北国先天下</t>
+          <t>理想汽车长沙万象城零售中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -17459,29 +17459,29 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
+          <t>理想汽车东莞麻涌交付中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>理想汽车东莞高埗交付中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -17491,29 +17491,29 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 75%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙君尚零售展厅</t>
+          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙万象城零售中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -17523,29 +17523,29 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞麻涌交付中心</t>
+          <t>华为智能生活馆•保定先天下</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞高埗交付中心</t>
+          <t>华为智能生活馆•保定北国先天下</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -17555,7 +17555,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 75%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -11219,7 +11219,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创茂）</t>
+          <t>华为智能生活馆•青岛金狮广场</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -11234,12 +11234,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号</t>
+          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛金狮广场</t>
+          <t>华为授权体验店（融创茂）</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
+          <t>山东省青岛市黄岛区滨海大道2777号</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -13193,7 +13193,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>广州白云万达新能源空间</t>
+          <t>广州森那美富悦4S中心</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -13208,12 +13208,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市白云区三元里街道云城东路501号</t>
+          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>连续在档 2 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13225,7 +13225,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>广州保利时光里新能源空间</t>
+          <t>广州白云万达新能源空间</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -13240,12 +13240,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
+          <t>广东省广州市白云区三元里街道云城东路501号</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -13257,7 +13257,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>广州森那美富悦4S中心</t>
+          <t>广州保利时光里新能源空间</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -13272,7 +13272,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
+          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>深圳星河WORLD.COCO Park新能源空间</t>
+          <t>深圳标林卫星店</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
+          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>深圳标林卫星店</t>
+          <t>深圳星河WORLD.COCO Park新能源空间</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>苏州吴江吾悦广场新能源空间</t>
+          <t>昆山青阳万达广场新能源空间</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -13528,12 +13528,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
+          <t>苏州市昆山市青阳北路234号</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13545,7 +13545,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>昆山青阳万达广场新能源空间</t>
+          <t>苏州吴江吾悦广场新能源空间</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>苏州市昆山市青阳北路234号</t>
+          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -15162,22 +15162,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -15187,29 +15187,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -15219,29 +15219,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -15251,29 +15251,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -15283,7 +15283,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
@@ -15295,17 +15295,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -15315,29 +15315,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -15347,29 +15347,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -15379,29 +15379,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -15411,29 +15411,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -15443,7 +15443,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
@@ -15455,17 +15455,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -15475,29 +15475,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15507,29 +15507,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15539,29 +15539,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15571,29 +15571,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15603,29 +15603,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -15635,29 +15635,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
@@ -15679,17 +15679,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -15699,29 +15699,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15731,29 +15731,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -15763,29 +15763,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -15795,7 +15795,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
@@ -15807,17 +15807,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -15827,7 +15827,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
@@ -15839,17 +15839,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -15859,29 +15859,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -15891,29 +15891,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -15923,7 +15923,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
@@ -15935,17 +15935,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -15955,29 +15955,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -15987,29 +15987,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -16019,29 +16019,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
     </row>
@@ -16063,17 +16063,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -16083,29 +16083,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -16115,7 +16115,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
     </row>
@@ -16154,22 +16154,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -16179,29 +16179,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -16211,29 +16211,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -16250,7 +16250,7 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -16260,12 +16260,12 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -16287,17 +16287,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都成双大道</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -16319,17 +16319,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -16351,17 +16351,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -16383,17 +16383,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -16415,17 +16415,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -16452,12 +16452,12 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16479,17 +16479,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -16506,22 +16506,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16538,22 +16538,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16570,22 +16570,22 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -16602,22 +16602,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -16634,22 +16634,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16671,17 +16671,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16698,22 +16698,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16735,17 +16735,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16767,17 +16767,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -16799,17 +16799,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16826,22 +16826,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -16863,17 +16863,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -16895,17 +16895,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16927,17 +16927,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -16954,22 +16954,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -16986,22 +16986,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -17018,22 +17018,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -17055,17 +17055,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -17082,22 +17082,22 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -17114,22 +17114,22 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -17146,22 +17146,22 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -17178,22 +17178,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -17215,17 +17215,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -17242,22 +17242,22 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -17274,22 +17274,22 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -17311,17 +17311,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -17343,17 +17343,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -17370,22 +17370,22 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店</t>
+          <t>华为授权体验店（东阳新光汇）</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店L141</t>
+          <t>华为授权体验店（见大未来天地）</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -17395,29 +17395,29 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 70%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东阳新光汇）</t>
+          <t>赣州万象城体验店</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（见大未来天地）</t>
+          <t>赣州万象城体验店L141</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -17427,29 +17427,29 @@
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 70%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙君尚零售展厅</t>
+          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙万象城零售中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -17459,7 +17459,7 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>
@@ -17498,22 +17498,22 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
+          <t>理想汽车长沙君尚零售展厅</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>理想汽车长沙万象城零售中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -17523,7 +17523,7 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -12201,7 +12201,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>西红门镇金时大街7号院3号楼一层101</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>西红门镇金时大街7号院3号楼一层101</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>广州森那美富悦4S中心</t>
+          <t>广州白云万达新能源空间</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -13208,12 +13208,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
+          <t>广东省广州市白云区三元里街道云城东路501号</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -13225,7 +13225,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>广州白云万达新能源空间</t>
+          <t>广州保利时光里新能源空间</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -13240,12 +13240,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市白云区三元里街道云城东路501号</t>
+          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>连续在档 2 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13257,7 +13257,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>广州保利时光里新能源空间</t>
+          <t>广州森那美富悦4S中心</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -13272,7 +13272,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
+          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -14601,7 +14601,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海金桥啦啦宝都</t>
+          <t>蔚来空间 | 上海徐汇万科广场</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -14616,7 +14616,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
+          <t>上海市徐汇区沪闵路9191号L1-17室</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海徐汇万科广场</t>
+          <t>蔚来空间 | 上海金桥啦啦宝都</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>上海市徐汇区沪闵路9191号L1-17室</t>
+          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -15167,17 +15167,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -15187,29 +15187,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -15219,29 +15219,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -15251,29 +15251,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
+          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -15283,7 +15283,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
@@ -15300,12 +15300,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -15315,29 +15315,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
@@ -15359,17 +15359,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -15379,29 +15379,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -15411,29 +15411,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -15443,29 +15443,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -15475,7 +15475,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
@@ -15519,17 +15519,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15539,7 +15539,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
@@ -15551,17 +15551,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15571,7 +15571,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
@@ -15583,17 +15583,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15603,29 +15603,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -15635,29 +15635,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15667,29 +15667,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -15699,7 +15699,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
@@ -15711,17 +15711,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15731,29 +15731,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -15763,29 +15763,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -15795,29 +15795,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -15827,14 +15827,14 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -15844,12 +15844,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -15859,7 +15859,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
@@ -15871,17 +15871,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -15891,29 +15891,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -15923,7 +15923,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
@@ -15935,17 +15935,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -15955,29 +15955,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -15987,29 +15987,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -16019,29 +16019,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -16051,29 +16051,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -16083,29 +16083,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -16115,7 +16115,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
     </row>
@@ -16127,17 +16127,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -16147,7 +16147,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
     </row>
@@ -16159,17 +16159,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -16179,29 +16179,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
+          <t>理想汽车景德镇国大汽车城零售展厅</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -16211,29 +16211,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -16255,17 +16255,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -16282,22 +16282,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -16319,17 +16319,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -16383,17 +16383,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -16415,17 +16415,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -16442,22 +16442,22 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16506,22 +16506,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16538,22 +16538,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16570,22 +16570,22 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -16607,17 +16607,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -16634,22 +16634,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16671,17 +16671,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16703,17 +16703,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16735,17 +16735,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16767,17 +16767,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -16799,17 +16799,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16826,22 +16826,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -16863,17 +16863,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -16890,22 +16890,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16927,17 +16927,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -16959,17 +16959,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -16986,22 +16986,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -17023,17 +17023,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -17050,22 +17050,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -17087,17 +17087,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -17114,22 +17114,22 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -17178,22 +17178,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -17215,17 +17215,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -17247,17 +17247,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -17274,22 +17274,22 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -17306,22 +17306,22 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -17338,22 +17338,22 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都成双大道</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -17434,22 +17434,22 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
+          <t>华为智能生活馆•保定先天下</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>华为智能生活馆•保定北国先天下</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -17459,7 +17459,7 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -17498,22 +17498,22 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙君尚零售展厅</t>
+          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙万象城零售中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -17523,29 +17523,29 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定先天下</t>
+          <t>理想汽车长沙君尚零售展厅</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定北国先天下</t>
+          <t>理想汽车长沙万象城零售中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -17555,7 +17555,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -12201,7 +12201,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>西红门镇金时大街7号院3号楼一层101</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>西红门镇金时大街7号院3号楼一层101</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>深圳标林卫星店</t>
+          <t>深圳星河WORLD.COCO Park新能源空间</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>深圳星河WORLD.COCO Park新能源空间</t>
+          <t>深圳标林卫星店</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
+          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>昆山青阳万达广场新能源空间</t>
+          <t>苏州吴江吾悦广场新能源空间</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -13528,12 +13528,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>苏州市昆山市青阳北路234号</t>
+          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -13545,7 +13545,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>苏州吴江吾悦广场新能源空间</t>
+          <t>昆山青阳万达广场新能源空间</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
+          <t>苏州市昆山市青阳北路234号</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海徐汇万科广场</t>
+          <t>蔚来空间 | 上海金桥啦啦宝都</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -14616,7 +14616,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>上海市徐汇区沪闵路9191号L1-17室</t>
+          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海金桥啦啦宝都</t>
+          <t>蔚来空间 | 上海徐汇万科广场</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
+          <t>上海市徐汇区沪闵路9191号L1-17室</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -15162,22 +15162,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -15187,29 +15187,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -15219,29 +15219,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
@@ -15263,17 +15263,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -15283,7 +15283,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
         </is>
       </c>
     </row>
@@ -15295,17 +15295,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -15315,29 +15315,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -15347,29 +15347,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -15379,29 +15379,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -15411,29 +15411,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -15443,29 +15443,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -15475,14 +15475,14 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -15492,12 +15492,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15507,29 +15507,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15539,29 +15539,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15571,7 +15571,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
@@ -15583,17 +15583,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15603,7 +15603,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
@@ -15642,22 +15642,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15667,29 +15667,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -15699,29 +15699,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15731,29 +15731,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -15763,29 +15763,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -15795,29 +15795,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -15827,14 +15827,14 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -15844,12 +15844,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -15859,29 +15859,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -15891,7 +15891,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
@@ -15903,17 +15903,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -15923,7 +15923,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
@@ -15935,17 +15935,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
@@ -15967,17 +15967,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -15987,29 +15987,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
@@ -16031,17 +16031,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售展厅</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
     </row>
@@ -16191,17 +16191,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -16211,29 +16211,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -16255,17 +16255,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -16282,22 +16282,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -16319,17 +16319,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都成双大道</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -16351,17 +16351,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -16383,17 +16383,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -16415,17 +16415,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -16442,22 +16442,22 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16474,22 +16474,22 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -16506,22 +16506,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16538,22 +16538,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16575,17 +16575,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -16602,22 +16602,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -16634,22 +16634,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16676,12 +16676,12 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16698,22 +16698,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16735,17 +16735,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16767,17 +16767,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -16799,17 +16799,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16831,17 +16831,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -16858,22 +16858,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -16890,22 +16890,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16922,22 +16922,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -16959,17 +16959,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -16991,17 +16991,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -17018,22 +17018,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -17050,22 +17050,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -17082,22 +17082,22 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -17119,17 +17119,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -17146,22 +17146,22 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -17188,12 +17188,12 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -17210,22 +17210,22 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -17242,22 +17242,22 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -17279,17 +17279,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -17306,22 +17306,22 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -17338,22 +17338,22 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -17370,22 +17370,22 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东阳新光汇）</t>
+          <t>赣州万象城体验店</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（见大未来天地）</t>
+          <t>赣州万象城体验店L141</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -17395,29 +17395,29 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 70%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店</t>
+          <t>华为授权体验店（东阳新光汇）</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店L141</t>
+          <t>华为授权体验店（见大未来天地）</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -17427,29 +17427,29 @@
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 70%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定先天下</t>
+          <t>理想汽车东莞麻涌交付中心</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定北国先天下</t>
+          <t>理想汽车东莞高埗交付中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -17459,29 +17459,29 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 75%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞麻涌交付中心</t>
+          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞高埗交付中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -17491,29 +17491,29 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 75%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
+          <t>华为智能生活馆•保定先天下</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>华为智能生活馆•保定北国先天下</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -17523,7 +17523,7 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -11219,7 +11219,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛金狮广场</t>
+          <t>华为授权体验店（融创茂）</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -11234,12 +11234,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
+          <t>山东省青岛市黄岛区滨海大道2777号</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创茂）</t>
+          <t>华为智能生活馆•青岛金狮广场</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号</t>
+          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -12201,7 +12201,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>西红门镇金时大街7号院3号楼一层101</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>西红门镇金时大街7号院3号楼一层101</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -12297,7 +12297,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市宝安区机场综合楼服务中心</t>
+          <t>小米汽车广东深圳宝安区沙井京基百纳</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车交付中心(机场综合楼店)</t>
+          <t>沙井京基百纳广场一楼橙厅</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期；本期存在高相似店名「小米汽车广东省深圳市宝安区机场综合楼零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区沙井京基百纳</t>
+          <t>小米汽车广东省深圳市宝安区机场综合楼服务中心</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -12344,12 +12344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>沙井京基百纳广场一楼橙厅</t>
+          <t>小米汽车交付中心(机场综合楼店)</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「小米汽车广东省深圳市宝安区机场综合楼零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>成都东安天街城市中心店</t>
+          <t>成都高新宜家家居新能源空间</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
+          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>成都高新宜家家居新能源空间</t>
+          <t>成都东安天街城市中心店</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
+          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -13289,7 +13289,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>深圳德顺行龙岗卫星店</t>
+          <t>深圳星河WORLD.COCO Park新能源空间</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>深圳星河WORLD.COCO Park新能源空间</t>
+          <t>深圳标林卫星店</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
+          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>深圳标林卫星店</t>
+          <t>深圳德顺行龙岗卫星店</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
+          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -14601,7 +14601,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海金桥啦啦宝都</t>
+          <t>蔚来空间 | 上海徐汇万科广场</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -14616,7 +14616,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
+          <t>上海市徐汇区沪闵路9191号L1-17室</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海徐汇万科广场</t>
+          <t>蔚来空间 | 上海金桥啦啦宝都</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>上海市徐汇区沪闵路9191号L1-17室</t>
+          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -15162,22 +15162,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -15187,29 +15187,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
@@ -15231,17 +15231,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -15251,29 +15251,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -15283,7 +15283,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
@@ -15295,17 +15295,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -15315,7 +15315,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
@@ -15327,17 +15327,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -15347,29 +15347,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
         </is>
       </c>
     </row>
@@ -15391,17 +15391,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -15411,29 +15411,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -15443,14 +15443,14 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -15460,12 +15460,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -15475,7 +15475,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
@@ -15514,22 +15514,22 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15539,29 +15539,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15571,7 +15571,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
@@ -15583,17 +15583,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15603,29 +15603,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -15635,29 +15635,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15667,29 +15667,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -15699,7 +15699,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
@@ -15711,17 +15711,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15731,7 +15731,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
@@ -15743,17 +15743,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -15763,7 +15763,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
@@ -15802,22 +15802,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -15827,29 +15827,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -15859,29 +15859,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -15891,7 +15891,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
@@ -15903,17 +15903,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -15923,7 +15923,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
@@ -15935,17 +15935,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -15955,29 +15955,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -15987,29 +15987,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
@@ -16031,17 +16031,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -16051,29 +16051,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -16083,29 +16083,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -16115,7 +16115,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
     </row>
@@ -16127,17 +16127,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售展厅</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -16147,7 +16147,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
     </row>
@@ -16159,17 +16159,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -16179,7 +16179,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
@@ -16191,17 +16191,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
     </row>
@@ -16223,17 +16223,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -16250,22 +16250,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -16287,17 +16287,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -16319,17 +16319,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -16351,17 +16351,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都成双大道</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -16383,17 +16383,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -16415,17 +16415,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -16442,22 +16442,22 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16474,22 +16474,22 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -16506,22 +16506,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16538,22 +16538,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16575,17 +16575,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -16602,22 +16602,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -16634,22 +16634,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16671,17 +16671,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16698,22 +16698,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16730,22 +16730,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16767,17 +16767,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -16794,22 +16794,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16831,17 +16831,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -16858,22 +16858,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -16895,17 +16895,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16927,17 +16927,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -16959,17 +16959,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -16986,22 +16986,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -17018,22 +17018,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -17055,17 +17055,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -17082,22 +17082,22 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -17119,17 +17119,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -17151,17 +17151,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -17178,22 +17178,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -17210,22 +17210,22 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -17242,22 +17242,22 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -17279,17 +17279,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -17306,22 +17306,22 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -17338,22 +17338,22 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -17439,17 +17439,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞麻涌交付中心</t>
+          <t>理想汽车长沙君尚零售展厅</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞高埗交付中心</t>
+          <t>理想汽车长沙万象城零售中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -17459,7 +17459,7 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 75%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
@@ -17498,22 +17498,22 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定先天下</t>
+          <t>理想汽车东莞麻涌交付中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定北国先天下</t>
+          <t>理想汽车东莞高埗交付中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -17523,29 +17523,29 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 75%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙君尚零售展厅</t>
+          <t>华为智能生活馆•保定先天下</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙万象城零售中心</t>
+          <t>华为智能生活馆•保定北国先天下</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -17555,7 +17555,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -12201,7 +12201,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>西红门镇金时大街7号院3号楼一层101</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>西红门镇金时大街7号院3号楼一层101</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>成都高新宜家家居新能源空间</t>
+          <t>成都东安天街城市中心店</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
+          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>成都东安天街城市中心店</t>
+          <t>成都高新宜家家居新能源空间</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
+          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -13289,7 +13289,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>深圳星河WORLD.COCO Park新能源空间</t>
+          <t>深圳标林卫星店</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
+          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>深圳标林卫星店</t>
+          <t>深圳星河WORLD.COCO Park新能源空间</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>苏州吴江吾悦广场新能源空间</t>
+          <t>昆山青阳万达广场新能源空间</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -13528,12 +13528,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
+          <t>苏州市昆山市青阳北路234号</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13545,7 +13545,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>昆山青阳万达广场新能源空间</t>
+          <t>苏州吴江吾悦广场新能源空间</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>苏州市昆山市青阳北路234号</t>
+          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海徐汇万科广场</t>
+          <t>蔚来空间 | 上海金桥啦啦宝都</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -14616,7 +14616,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>上海市徐汇区沪闵路9191号L1-17室</t>
+          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海金桥啦啦宝都</t>
+          <t>蔚来空间 | 上海徐汇万科广场</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
+          <t>上海市徐汇区沪闵路9191号L1-17室</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -15162,22 +15162,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -15187,7 +15187,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
@@ -15199,17 +15199,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
@@ -15231,17 +15231,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -15251,29 +15251,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -15283,7 +15283,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
@@ -15295,17 +15295,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -15315,29 +15315,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
@@ -15386,22 +15386,22 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
@@ -15450,22 +15450,22 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -15475,7 +15475,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
@@ -15487,17 +15487,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15507,29 +15507,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15539,29 +15539,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15571,29 +15571,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15603,29 +15603,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -15635,29 +15635,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15667,29 +15667,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -15699,29 +15699,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15731,29 +15731,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -15763,7 +15763,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
@@ -15802,22 +15802,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -15827,29 +15827,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -15859,29 +15859,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -15891,29 +15891,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -15923,7 +15923,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
@@ -15935,17 +15935,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -15955,29 +15955,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -15987,29 +15987,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -16019,29 +16019,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -16051,29 +16051,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -16083,29 +16083,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
+          <t>理想汽车景德镇国大汽车城零售展厅</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -16115,7 +16115,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
     </row>
@@ -16127,17 +16127,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -16147,29 +16147,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -16179,7 +16179,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
     </row>
@@ -16223,17 +16223,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -16250,22 +16250,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -16287,17 +16287,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -16314,22 +16314,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -16351,17 +16351,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -16383,17 +16383,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -16415,17 +16415,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -16442,22 +16442,22 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16474,22 +16474,22 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -16506,22 +16506,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16538,22 +16538,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16580,12 +16580,12 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -16607,17 +16607,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -16634,22 +16634,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16666,22 +16666,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16703,17 +16703,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16735,17 +16735,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16762,22 +16762,22 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -16794,22 +16794,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16826,22 +16826,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -16858,22 +16858,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -16895,17 +16895,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16922,22 +16922,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -16959,17 +16959,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -16986,22 +16986,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -17018,22 +17018,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -17055,17 +17055,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -17087,17 +17087,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -17119,17 +17119,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -17156,12 +17156,12 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -17178,22 +17178,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -17210,22 +17210,22 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -17247,17 +17247,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -17279,17 +17279,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -17306,22 +17306,22 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -17338,22 +17338,22 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都成双大道</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -17370,22 +17370,22 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店</t>
+          <t>华为授权体验店（东阳新光汇）</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店L141</t>
+          <t>华为授权体验店（见大未来天地）</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -17395,29 +17395,29 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 70%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东阳新光汇）</t>
+          <t>赣州万象城体验店</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（见大未来天地）</t>
+          <t>赣州万象城体验店L141</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -17427,29 +17427,29 @@
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 70%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙君尚零售展厅</t>
+          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙万象城零售中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -17459,29 +17459,29 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
+          <t>华为智能生活馆•保定先天下</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>华为智能生活馆•保定北国先天下</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -17530,22 +17530,22 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定先天下</t>
+          <t>理想汽车长沙君尚零售展厅</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定北国先天下</t>
+          <t>理想汽车长沙万象城零售中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -17555,7 +17555,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
